--- a/artfynd/A 31729-2026 artfynd.xlsx
+++ b/artfynd/A 31729-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136408759</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136408857</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136408874</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136408962</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136408981</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136409088</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136409123</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136409159</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136409187</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136410254</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136410271</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>136409404</v>
       </c>
       <c r="B13" t="n">
-        <v>80469</v>
+        <v>80482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136409071</v>
       </c>
       <c r="B14" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>136409389</v>
       </c>
       <c r="B15" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>136408777</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136408891</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>136409415</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>136410240</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>136410283</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>136410779</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31729-2026 artfynd.xlsx
+++ b/artfynd/A 31729-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136408759</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136408857</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136408874</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136408962</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136408981</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136409088</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136409123</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136409159</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136409187</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136410254</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>136410271</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>136409404</v>
       </c>
       <c r="B13" t="n">
-        <v>80482</v>
+        <v>80483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
